--- a/outputs/tables/tabla_esda_moran.xlsx
+++ b/outputs/tables/tabla_esda_moran.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Métrica</t>
   </si>
@@ -29,7 +29,10 @@
     <t>Número de Observaciones (N)</t>
   </si>
   <si>
-    <t>Número de Islas (Aislados)</t>
+    <t>Islas Iniciales (sin conectar)</t>
+  </si>
+  <si>
+    <t>Islas Finales (conectadas)</t>
   </si>
   <si>
     <t>Promedio de Vecinos</t>
@@ -414,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -455,10 +458,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>4.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -466,10 +469,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>212.9804</v>
+        <v>5.25</v>
       </c>
       <c r="C5">
-        <v>193.8323</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -477,10 +480,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>214.996</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>195.8479</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -488,10 +491,21 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -509,20 +523,20 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>0.1730125277170391</v>
+        <v>0.110273006567433</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>-0.00411522633744856</v>
@@ -530,18 +544,18 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>4.364025079834273</v>
+        <v>2.827688683475972</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>0.0004</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_esda_moran.xlsx
+++ b/outputs/tables/tabla_esda_moran.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Métrica</t>
   </si>
@@ -47,6 +47,15 @@
     <t>Mínimo número de vecinos</t>
   </si>
   <si>
+    <t>Matriz Seleccionada para el Modelo Final</t>
+  </si>
+  <si>
+    <t>SÍ (Queen, 4 islas de Puná conectadas)</t>
+  </si>
+  <si>
+    <t>NO (Descartada)</t>
+  </si>
+  <si>
     <t>Valor</t>
   </si>
   <si>
@@ -59,7 +68,22 @@
     <t>Z-Score</t>
   </si>
   <si>
-    <t>Pseudo p-valor (9999 perm)</t>
+    <t>Pseudo p-valor</t>
+  </si>
+  <si>
+    <t>Permutaciones</t>
+  </si>
+  <si>
+    <t>Semilla Aleatoria</t>
+  </si>
+  <si>
+    <t>Matriz Espacial Utilizada</t>
+  </si>
+  <si>
+    <t>Promedio Vecinos Matriz</t>
+  </si>
+  <si>
+    <t>Queen (4 islas de Puná conectadas)</t>
   </si>
 </sst>
 </file>
@@ -417,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -480,10 +504,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>214.996</v>
+        <v>2.15</v>
       </c>
       <c r="C6">
-        <v>195.8479</v>
+        <v>1.9585</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -506,6 +530,17 @@
       </c>
       <c r="C8">
         <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -515,7 +550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -523,39 +558,71 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2">
-        <v>0.110273006567433</v>
+        <v>0.1103</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3">
-        <v>-0.00411522633744856</v>
+        <v>-0.0041</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>2.827688683475972</v>
+        <v>2.8277</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>0.007900000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_esda_moran.xlsx
+++ b/outputs/tables/tabla_esda_moran.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Métrica</t>
   </si>
@@ -56,34 +56,58 @@
     <t>NO (Descartada)</t>
   </si>
   <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Indice Moran I</t>
-  </si>
-  <si>
-    <t>Esperanza E(I)</t>
-  </si>
-  <si>
-    <t>Z-Score</t>
-  </si>
-  <si>
-    <t>Pseudo p-valor</t>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Indice_Moran_I</t>
+  </si>
+  <si>
+    <t>Esperanza_EI</t>
+  </si>
+  <si>
+    <t>Z_Score</t>
+  </si>
+  <si>
+    <t>Pseudo_p_valor</t>
   </si>
   <si>
     <t>Permutaciones</t>
   </si>
   <si>
-    <t>Semilla Aleatoria</t>
-  </si>
-  <si>
-    <t>Matriz Espacial Utilizada</t>
-  </si>
-  <si>
-    <t>Promedio Vecinos Matriz</t>
+    <t>Semilla</t>
+  </si>
+  <si>
+    <t>Matriz_Espacial</t>
+  </si>
+  <si>
+    <t>Promedio_Vecinos</t>
+  </si>
+  <si>
+    <t>Rol_en_Tesis</t>
+  </si>
+  <si>
+    <t>(a) Periodo del Modelo (Principal)</t>
+  </si>
+  <si>
+    <t>(b) Periodo Completo (Exploratorio)</t>
+  </si>
+  <si>
+    <t>Homicidios 2024-2025</t>
+  </si>
+  <si>
+    <t>Homicidios 2024-2026 (Total)</t>
   </si>
   <si>
     <t>Queen (4 islas de Puná conectadas)</t>
+  </si>
+  <si>
+    <t>Texto principal de la tesis (Capítulos 3 y 4)</t>
+  </si>
+  <si>
+    <t>Análisis exploratorio complementario</t>
   </si>
 </sst>
 </file>
@@ -550,79 +574,112 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>0.1149</v>
+      </c>
+      <c r="D2">
+        <v>-0.0041</v>
+      </c>
+      <c r="E2">
+        <v>2.9487</v>
+      </c>
+      <c r="F2">
+        <v>0.0062</v>
+      </c>
+      <c r="G2">
+        <v>9999</v>
+      </c>
+      <c r="H2">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2">
+        <v>5.25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3">
         <v>0.1103</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3">
+      <c r="D3">
         <v>-0.0041</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
+      <c r="E3">
         <v>2.8277</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5">
+      <c r="F3">
         <v>0.007900000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
+      <c r="G3">
         <v>9999</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
+      <c r="H3">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3">
         <v>5.25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
